--- a/eval/eval_set_review.xlsx
+++ b/eval/eval_set_review.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="평가셋" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="평가셋" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'평가셋'!$A$1:$Q$73</definedName>
@@ -3146,10 +3146,16 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>(v1과 같음)</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr"/>
+          <t>멘토링 외 개별 만남은 금지다. 필요하면 운영사무국에 사전 연락하거나 정서지지 멘토링 등 프로그램을 이용한다. 4회차 이상 진행한 그룹은 멘티 보호자의 사전동의를 받고 친화·성장활동을 신청해 승인받아 진행할 수 있다.</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>manual-2026-3-1:35
+manual-2026-5-2:57
+notice-2026-n11</t>
+        </is>
+      </c>
       <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
@@ -4148,10 +4154,16 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>(v1과 같음)</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr"/>
+          <t>성장활동으로 승인받으면 오프라인 2시간으로 인정돼 6만 원이 지급된다(봉사시간·가산금 없음). 4회차 이상 진행한 그룹이 멘티 보호자의 사전동의를 받은 뒤 활동 5일 전까지 구글폼으로 신청하고, 승인 여부는 3~5일 이내 문자로 안내받는다. 활동 후 7일 이내에 시작·내용·종료 사진 3종을 하나의 파일로 압축해 결과보고서와 함께 낸다. 회기별 유형당 1회만 가능하다.</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>manual-2026-5-2:57
+manual-2026-5-2:58
+notice-2026-n11</t>
+        </is>
+      </c>
       <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="3" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr"/>
@@ -4207,10 +4219,15 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>(v1과 같음)</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr"/>
+          <t>안 된다. 학습 멘토링을 포함한 모든 멘토링 활동은 같은 날짜에 진행할 수 없다.</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>manual-2026-5-2:58
+notice-2026-n11</t>
+        </is>
+      </c>
       <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="3" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr"/>
@@ -4666,11 +4683,20 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>(v1과 같음)</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr"/>
-      <c r="M67" s="3" t="inlineStr"/>
+          <t>매뉴얼과 공지에는 봉사시간 인정 기준이 없고, 친화·성장활동은 봉사시간 인정이 불가하다는 내용만 있다. 운영사무국에 문의한다.</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>manual-2026-5-2:57
+notice-2026-n11</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>운영사무국</t>
+        </is>
+      </c>
       <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr"/>
       <c r="P67" s="3" t="inlineStr"/>
